--- a/main/upload/upload.xlsx
+++ b/main/upload/upload.xlsx
@@ -1845,7 +1845,6 @@
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1862,14 +1861,11 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -2160,7 +2156,7 @@
       <c r="C2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E2" s="1">
@@ -2204,7 +2200,7 @@
       <c r="C3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E3" s="1">
@@ -2248,7 +2244,7 @@
       <c r="C4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="1">
@@ -2292,7 +2288,7 @@
       <c r="C5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E5" s="1">
@@ -2336,7 +2332,7 @@
       <c r="C6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E6" s="1">
@@ -2380,7 +2376,7 @@
       <c r="C7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E7" s="1">
@@ -2424,7 +2420,7 @@
       <c r="C8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>40</v>
       </c>
       <c r="E8" s="1">
@@ -2468,7 +2464,7 @@
       <c r="C9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E9" s="1">
@@ -2512,7 +2508,7 @@
       <c r="C10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E10" s="1">
@@ -2556,7 +2552,7 @@
       <c r="C11" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E11" s="1">
@@ -2600,7 +2596,7 @@
       <c r="C12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>52</v>
       </c>
       <c r="E12" s="1">
@@ -2644,7 +2640,7 @@
       <c r="C13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E13" s="1">
@@ -2688,7 +2684,7 @@
       <c r="C14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E14" s="1">
@@ -2732,7 +2728,7 @@
       <c r="C15" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>61</v>
       </c>
       <c r="E15" s="1">
@@ -2776,7 +2772,7 @@
       <c r="C16" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>64</v>
       </c>
       <c r="E16" s="1">
@@ -2820,7 +2816,7 @@
       <c r="C17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>67</v>
       </c>
       <c r="E17" s="1">
@@ -2864,7 +2860,7 @@
       <c r="C18" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>70</v>
       </c>
       <c r="E18" s="1">
@@ -2908,7 +2904,7 @@
       <c r="C19" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>73</v>
       </c>
       <c r="E19" s="1">
@@ -2952,7 +2948,7 @@
       <c r="C20" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="1" t="s">
         <v>76</v>
       </c>
       <c r="E20" s="1">
@@ -2996,7 +2992,7 @@
       <c r="C21" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>79</v>
       </c>
       <c r="E21" s="1">
@@ -3040,7 +3036,7 @@
       <c r="C22" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
         <v>82</v>
       </c>
       <c r="E22" s="1">
@@ -3084,7 +3080,7 @@
       <c r="C23" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>85</v>
       </c>
       <c r="E23" s="1">
@@ -3128,7 +3124,7 @@
       <c r="C24" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="1" t="s">
         <v>89</v>
       </c>
       <c r="E24" s="1">
@@ -3172,7 +3168,7 @@
       <c r="C25" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="1" t="s">
         <v>92</v>
       </c>
       <c r="E25" s="1">
@@ -3216,7 +3212,7 @@
       <c r="C26" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="1" t="s">
         <v>95</v>
       </c>
       <c r="E26" s="1">
@@ -3260,7 +3256,7 @@
       <c r="C27" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="1" t="s">
         <v>98</v>
       </c>
       <c r="E27" s="1">
@@ -3304,7 +3300,7 @@
       <c r="C28" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="1" t="s">
         <v>101</v>
       </c>
       <c r="E28" s="1">
@@ -3348,7 +3344,7 @@
       <c r="C29" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="1" t="s">
         <v>104</v>
       </c>
       <c r="E29" s="1">
@@ -3392,7 +3388,7 @@
       <c r="C30" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="1" t="s">
         <v>107</v>
       </c>
       <c r="E30" s="1">
@@ -3436,7 +3432,7 @@
       <c r="C31" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="1" t="s">
         <v>110</v>
       </c>
       <c r="E31" s="1">
@@ -3480,7 +3476,7 @@
       <c r="C32" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="1" t="s">
         <v>113</v>
       </c>
       <c r="E32" s="1">
@@ -3524,7 +3520,7 @@
       <c r="C33" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="1" t="s">
         <v>116</v>
       </c>
       <c r="E33" s="1">
@@ -3568,7 +3564,7 @@
       <c r="C34" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="1" t="s">
         <v>119</v>
       </c>
       <c r="E34" s="1">
@@ -3612,7 +3608,7 @@
       <c r="C35" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="1" t="s">
         <v>122</v>
       </c>
       <c r="E35" s="1">
@@ -3656,7 +3652,7 @@
       <c r="C36" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="1" t="s">
         <v>125</v>
       </c>
       <c r="E36" s="1">
@@ -3700,7 +3696,7 @@
       <c r="C37" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E37" s="1">
@@ -3744,7 +3740,7 @@
       <c r="C38" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="1" t="s">
         <v>131</v>
       </c>
       <c r="E38" s="1">
@@ -3788,7 +3784,7 @@
       <c r="C39" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="1" t="s">
         <v>134</v>
       </c>
       <c r="E39" s="1">
@@ -3832,7 +3828,7 @@
       <c r="C40" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="1" t="s">
         <v>137</v>
       </c>
       <c r="E40" s="1">
@@ -3876,7 +3872,7 @@
       <c r="C41" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="1" t="s">
         <v>140</v>
       </c>
       <c r="E41" s="1">
@@ -3920,7 +3916,7 @@
       <c r="C42" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="1" t="s">
         <v>143</v>
       </c>
       <c r="E42" s="1">
@@ -3964,7 +3960,7 @@
       <c r="C43" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="1" t="s">
         <v>146</v>
       </c>
       <c r="E43" s="1">
@@ -4008,7 +4004,7 @@
       <c r="C44" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" s="1" t="s">
         <v>149</v>
       </c>
       <c r="E44" s="1">
@@ -4052,7 +4048,7 @@
       <c r="C45" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E45" s="1">
@@ -4096,7 +4092,7 @@
       <c r="C46" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="1" t="s">
         <v>156</v>
       </c>
       <c r="E46" s="1">
@@ -4140,7 +4136,7 @@
       <c r="C47" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="1" t="s">
         <v>160</v>
       </c>
       <c r="E47" s="1">
@@ -4184,7 +4180,7 @@
       <c r="C48" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="1" t="s">
         <v>163</v>
       </c>
       <c r="E48" s="1">
@@ -4228,7 +4224,7 @@
       <c r="C49" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="1" t="s">
         <v>166</v>
       </c>
       <c r="E49" s="1">
@@ -4272,7 +4268,7 @@
       <c r="C50" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="1" t="s">
         <v>169</v>
       </c>
       <c r="E50" s="1">
@@ -4316,7 +4312,7 @@
       <c r="C51" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="1" t="s">
         <v>172</v>
       </c>
       <c r="E51" s="1">
@@ -4360,7 +4356,7 @@
       <c r="C52" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="1" t="s">
         <v>175</v>
       </c>
       <c r="E52" s="1">
@@ -4404,7 +4400,7 @@
       <c r="C53" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="1" t="s">
         <v>178</v>
       </c>
       <c r="E53" s="1">
@@ -4448,7 +4444,7 @@
       <c r="C54" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D54" s="1" t="s">
         <v>181</v>
       </c>
       <c r="E54" s="1">
@@ -4492,7 +4488,7 @@
       <c r="C55" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" s="1" t="s">
         <v>184</v>
       </c>
       <c r="E55" s="1">
@@ -4536,7 +4532,7 @@
       <c r="C56" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D56" s="1" t="s">
         <v>187</v>
       </c>
       <c r="E56" s="1">
@@ -4580,7 +4576,7 @@
       <c r="C57" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D57" s="1" t="s">
         <v>190</v>
       </c>
       <c r="E57" s="1">
@@ -4624,7 +4620,7 @@
       <c r="C58" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D58" s="1" t="s">
         <v>193</v>
       </c>
       <c r="E58" s="1">
@@ -4668,7 +4664,7 @@
       <c r="C59" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D59" s="1" t="s">
         <v>196</v>
       </c>
       <c r="E59" s="1">
@@ -4712,7 +4708,7 @@
       <c r="C60" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D60" s="1" t="s">
         <v>199</v>
       </c>
       <c r="E60" s="1">
@@ -4756,7 +4752,7 @@
       <c r="C61" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D61" s="1" t="s">
         <v>202</v>
       </c>
       <c r="E61" s="1">
@@ -4800,7 +4796,7 @@
       <c r="C62" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D62" s="1" t="s">
         <v>205</v>
       </c>
       <c r="E62" s="1">
@@ -4844,7 +4840,7 @@
       <c r="C63" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="D63" s="1" t="s">
         <v>208</v>
       </c>
       <c r="E63" s="1">
@@ -4888,7 +4884,7 @@
       <c r="C64" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D64" s="1" t="s">
         <v>211</v>
       </c>
       <c r="E64" s="1">
@@ -4932,7 +4928,7 @@
       <c r="C65" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D65" s="1" t="s">
         <v>214</v>
       </c>
       <c r="E65" s="1">
@@ -4976,7 +4972,7 @@
       <c r="C66" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="D66" s="1" t="s">
         <v>217</v>
       </c>
       <c r="E66" s="1">
@@ -5020,7 +5016,7 @@
       <c r="C67" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="D67" s="1" t="s">
         <v>220</v>
       </c>
       <c r="E67" s="1">
@@ -5064,7 +5060,7 @@
       <c r="C68" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="D68" s="1" t="s">
         <v>223</v>
       </c>
       <c r="E68" s="1">
@@ -5108,7 +5104,7 @@
       <c r="C69" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="D69" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E69" s="1">
@@ -5152,7 +5148,7 @@
       <c r="C70" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="D70" s="1" t="s">
         <v>229</v>
       </c>
       <c r="E70" s="1">
@@ -5196,7 +5192,7 @@
       <c r="C71" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="D71" s="1" t="s">
         <v>232</v>
       </c>
       <c r="E71" s="1">
@@ -5240,7 +5236,7 @@
       <c r="C72" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="D72" s="1" t="s">
         <v>235</v>
       </c>
       <c r="E72" s="1">
@@ -5284,7 +5280,7 @@
       <c r="C73" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="D73" s="1" t="s">
         <v>238</v>
       </c>
       <c r="E73" s="1">
@@ -5328,7 +5324,7 @@
       <c r="C74" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="D74" s="1" t="s">
         <v>241</v>
       </c>
       <c r="E74" s="1">
@@ -5372,7 +5368,7 @@
       <c r="C75" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="D75" s="1" t="s">
         <v>244</v>
       </c>
       <c r="E75" s="1">
@@ -5416,7 +5412,7 @@
       <c r="C76" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="D76" s="1" t="s">
         <v>247</v>
       </c>
       <c r="E76" s="1">
@@ -5460,7 +5456,7 @@
       <c r="C77" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="D77" s="1" t="s">
         <v>250</v>
       </c>
       <c r="E77" s="1">
@@ -5504,7 +5500,7 @@
       <c r="C78" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="D78" s="1" t="s">
         <v>253</v>
       </c>
       <c r="E78" s="1">
@@ -5548,7 +5544,7 @@
       <c r="C79" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="D79" s="2" t="s">
+      <c r="D79" s="1" t="s">
         <v>256</v>
       </c>
       <c r="E79" s="1">
@@ -5592,7 +5588,7 @@
       <c r="C80" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="D80" s="1" t="s">
         <v>259</v>
       </c>
       <c r="E80" s="1">
@@ -5636,7 +5632,7 @@
       <c r="C81" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="D81" s="1" t="s">
         <v>262</v>
       </c>
       <c r="E81" s="1">
@@ -5680,7 +5676,7 @@
       <c r="C82" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="D82" s="2" t="s">
+      <c r="D82" s="1" t="s">
         <v>265</v>
       </c>
       <c r="E82" s="1">
@@ -5724,7 +5720,7 @@
       <c r="C83" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="D83" s="1" t="s">
         <v>268</v>
       </c>
       <c r="E83" s="1">
@@ -5768,7 +5764,7 @@
       <c r="C84" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="D84" s="1" t="s">
         <v>271</v>
       </c>
       <c r="E84" s="1">
@@ -5812,7 +5808,7 @@
       <c r="C85" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="D85" s="1" t="s">
         <v>274</v>
       </c>
       <c r="E85" s="1">
@@ -5856,7 +5852,7 @@
       <c r="C86" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="D86" s="1" t="s">
         <v>277</v>
       </c>
       <c r="E86" s="1">
@@ -5900,7 +5896,7 @@
       <c r="C87" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="D87" s="1" t="s">
         <v>280</v>
       </c>
       <c r="E87" s="1">
@@ -5944,7 +5940,7 @@
       <c r="C88" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="D88" s="1" t="s">
         <v>283</v>
       </c>
       <c r="E88" s="1">
@@ -5988,7 +5984,7 @@
       <c r="C89" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="D89" s="2" t="s">
+      <c r="D89" s="1" t="s">
         <v>286</v>
       </c>
       <c r="E89" s="1">
@@ -6032,7 +6028,7 @@
       <c r="C90" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="D90" s="2" t="s">
+      <c r="D90" s="1" t="s">
         <v>289</v>
       </c>
       <c r="E90" s="1">
@@ -6076,7 +6072,7 @@
       <c r="C91" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="D91" s="1" t="s">
         <v>292</v>
       </c>
       <c r="E91" s="1">
@@ -6120,7 +6116,7 @@
       <c r="C92" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="D92" s="2" t="s">
+      <c r="D92" s="1" t="s">
         <v>295</v>
       </c>
       <c r="E92" s="1">
@@ -6164,7 +6160,7 @@
       <c r="C93" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="D93" s="1" t="s">
         <v>298</v>
       </c>
       <c r="E93" s="1">
@@ -6208,7 +6204,7 @@
       <c r="C94" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="D94" s="2" t="s">
+      <c r="D94" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E94" s="1">
@@ -6252,7 +6248,7 @@
       <c r="C95" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="D95" s="2" t="s">
+      <c r="D95" s="1" t="s">
         <v>304</v>
       </c>
       <c r="E95" s="1">
@@ -6296,7 +6292,7 @@
       <c r="C96" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="D96" s="1" t="s">
         <v>307</v>
       </c>
       <c r="E96" s="1">
@@ -6340,7 +6336,7 @@
       <c r="C97" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="D97" s="1" t="s">
         <v>310</v>
       </c>
       <c r="E97" s="1">
@@ -6384,7 +6380,7 @@
       <c r="C98" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="D98" s="2" t="s">
+      <c r="D98" s="1" t="s">
         <v>313</v>
       </c>
       <c r="E98" s="1">
@@ -6428,7 +6424,7 @@
       <c r="C99" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="D99" s="2" t="s">
+      <c r="D99" s="1" t="s">
         <v>316</v>
       </c>
       <c r="E99" s="1">
@@ -6472,7 +6468,7 @@
       <c r="C100" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="D100" s="2" t="s">
+      <c r="D100" s="1" t="s">
         <v>319</v>
       </c>
       <c r="E100" s="1">
@@ -6516,7 +6512,7 @@
       <c r="C101" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="D101" s="2" t="s">
+      <c r="D101" s="1" t="s">
         <v>322</v>
       </c>
       <c r="E101" s="1">
@@ -6560,7 +6556,7 @@
       <c r="C102" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="D102" s="2" t="s">
+      <c r="D102" s="1" t="s">
         <v>325</v>
       </c>
       <c r="E102" s="1">
@@ -6604,7 +6600,7 @@
       <c r="C103" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="D103" s="2" t="s">
+      <c r="D103" s="1" t="s">
         <v>328</v>
       </c>
       <c r="E103" s="1">
@@ -6648,7 +6644,7 @@
       <c r="C104" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="D104" s="2" t="s">
+      <c r="D104" s="1" t="s">
         <v>331</v>
       </c>
       <c r="E104" s="1">
@@ -6692,7 +6688,7 @@
       <c r="C105" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="D105" s="2" t="s">
+      <c r="D105" s="1" t="s">
         <v>334</v>
       </c>
       <c r="E105" s="1">
@@ -6736,7 +6732,7 @@
       <c r="C106" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="D106" s="2" t="s">
+      <c r="D106" s="1" t="s">
         <v>337</v>
       </c>
       <c r="E106" s="1">
@@ -6780,7 +6776,7 @@
       <c r="C107" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="D107" s="2" t="s">
+      <c r="D107" s="1" t="s">
         <v>340</v>
       </c>
       <c r="E107" s="1">
@@ -6824,7 +6820,7 @@
       <c r="C108" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="D108" s="2" t="s">
+      <c r="D108" s="1" t="s">
         <v>343</v>
       </c>
       <c r="E108" s="1">
@@ -6868,7 +6864,7 @@
       <c r="C109" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="D109" s="2" t="s">
+      <c r="D109" s="1" t="s">
         <v>346</v>
       </c>
       <c r="E109" s="1">
@@ -6912,7 +6908,7 @@
       <c r="C110" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="D110" s="2" t="s">
+      <c r="D110" s="1" t="s">
         <v>349</v>
       </c>
       <c r="E110" s="1">
@@ -6956,7 +6952,7 @@
       <c r="C111" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="D111" s="2" t="s">
+      <c r="D111" s="1" t="s">
         <v>352</v>
       </c>
       <c r="E111" s="1">
@@ -7000,7 +6996,7 @@
       <c r="C112" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="D112" s="2" t="s">
+      <c r="D112" s="1" t="s">
         <v>355</v>
       </c>
       <c r="E112" s="1">
@@ -7044,7 +7040,7 @@
       <c r="C113" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="D113" s="2" t="s">
+      <c r="D113" s="1" t="s">
         <v>358</v>
       </c>
       <c r="E113" s="1">
@@ -7088,7 +7084,7 @@
       <c r="C114" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="D114" s="2" t="s">
+      <c r="D114" s="1" t="s">
         <v>361</v>
       </c>
       <c r="E114" s="1">
@@ -7132,7 +7128,7 @@
       <c r="C115" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="D115" s="2" t="s">
+      <c r="D115" s="1" t="s">
         <v>364</v>
       </c>
       <c r="E115" s="1">
@@ -7176,7 +7172,7 @@
       <c r="C116" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="D116" s="2" t="s">
+      <c r="D116" s="1" t="s">
         <v>367</v>
       </c>
       <c r="E116" s="1">
@@ -7220,7 +7216,7 @@
       <c r="C117" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="D117" s="2" t="s">
+      <c r="D117" s="1" t="s">
         <v>370</v>
       </c>
       <c r="E117" s="1">
@@ -7264,7 +7260,7 @@
       <c r="C118" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="D118" s="2" t="s">
+      <c r="D118" s="1" t="s">
         <v>373</v>
       </c>
       <c r="E118" s="1">
@@ -7308,7 +7304,7 @@
       <c r="C119" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="D119" s="2" t="s">
+      <c r="D119" s="1" t="s">
         <v>376</v>
       </c>
       <c r="E119" s="1">
@@ -7352,7 +7348,7 @@
       <c r="C120" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="D120" s="2" t="s">
+      <c r="D120" s="1" t="s">
         <v>379</v>
       </c>
       <c r="E120" s="1">
@@ -7396,7 +7392,7 @@
       <c r="C121" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="D121" s="2" t="s">
+      <c r="D121" s="1" t="s">
         <v>382</v>
       </c>
       <c r="E121" s="1">
@@ -7440,7 +7436,7 @@
       <c r="C122" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="D122" s="2" t="s">
+      <c r="D122" s="1" t="s">
         <v>385</v>
       </c>
       <c r="E122" s="1">
@@ -7484,7 +7480,7 @@
       <c r="C123" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="D123" s="2" t="s">
+      <c r="D123" s="1" t="s">
         <v>388</v>
       </c>
       <c r="E123" s="1">
@@ -7528,7 +7524,7 @@
       <c r="C124" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="D124" s="2" t="s">
+      <c r="D124" s="1" t="s">
         <v>391</v>
       </c>
       <c r="E124" s="1">
@@ -7572,7 +7568,7 @@
       <c r="C125" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="D125" s="2" t="s">
+      <c r="D125" s="1" t="s">
         <v>394</v>
       </c>
       <c r="E125" s="1">
@@ -7616,7 +7612,7 @@
       <c r="C126" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="D126" s="2" t="s">
+      <c r="D126" s="1" t="s">
         <v>397</v>
       </c>
       <c r="E126" s="1">
@@ -7660,7 +7656,7 @@
       <c r="C127" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="D127" s="2" t="s">
+      <c r="D127" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E127" s="1">
@@ -7704,7 +7700,7 @@
       <c r="C128" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="D128" s="2" t="s">
+      <c r="D128" s="1" t="s">
         <v>403</v>
       </c>
       <c r="E128" s="1">
@@ -7748,7 +7744,7 @@
       <c r="C129" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="D129" s="2" t="s">
+      <c r="D129" s="1" t="s">
         <v>406</v>
       </c>
       <c r="E129" s="1">
@@ -7792,7 +7788,7 @@
       <c r="C130" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="D130" s="2" t="s">
+      <c r="D130" s="1" t="s">
         <v>409</v>
       </c>
       <c r="E130" s="1">
@@ -7836,7 +7832,7 @@
       <c r="C131" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="D131" s="2" t="s">
+      <c r="D131" s="1" t="s">
         <v>412</v>
       </c>
       <c r="E131" s="1">
@@ -7880,7 +7876,7 @@
       <c r="C132" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="D132" s="2" t="s">
+      <c r="D132" s="1" t="s">
         <v>415</v>
       </c>
       <c r="E132" s="1">
@@ -7924,7 +7920,7 @@
       <c r="C133" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="D133" s="2" t="s">
+      <c r="D133" s="1" t="s">
         <v>418</v>
       </c>
       <c r="E133" s="1">
@@ -7968,7 +7964,7 @@
       <c r="C134" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="D134" s="2" t="s">
+      <c r="D134" s="1" t="s">
         <v>421</v>
       </c>
       <c r="E134" s="1">
@@ -8012,7 +8008,7 @@
       <c r="C135" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="D135" s="2" t="s">
+      <c r="D135" s="1" t="s">
         <v>424</v>
       </c>
       <c r="E135" s="1">
@@ -8056,7 +8052,7 @@
       <c r="C136" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="D136" s="2" t="s">
+      <c r="D136" s="1" t="s">
         <v>427</v>
       </c>
       <c r="E136" s="1">
@@ -8100,7 +8096,7 @@
       <c r="C137" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="D137" s="2" t="s">
+      <c r="D137" s="1" t="s">
         <v>430</v>
       </c>
       <c r="E137" s="1">
@@ -8144,7 +8140,7 @@
       <c r="C138" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="D138" s="2" t="s">
+      <c r="D138" s="1" t="s">
         <v>433</v>
       </c>
       <c r="E138" s="1">
@@ -8188,7 +8184,7 @@
       <c r="C139" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="D139" s="2" t="s">
+      <c r="D139" s="1" t="s">
         <v>436</v>
       </c>
       <c r="E139" s="1">
@@ -8232,7 +8228,7 @@
       <c r="C140" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="D140" s="2" t="s">
+      <c r="D140" s="1" t="s">
         <v>439</v>
       </c>
       <c r="E140" s="1">
@@ -8276,7 +8272,7 @@
       <c r="C141" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="D141" s="2" t="s">
+      <c r="D141" s="1" t="s">
         <v>442</v>
       </c>
       <c r="E141" s="1">
@@ -8320,7 +8316,7 @@
       <c r="C142" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="D142" s="2" t="s">
+      <c r="D142" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E142" s="1">
@@ -8364,7 +8360,7 @@
       <c r="C143" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="D143" s="2" t="s">
+      <c r="D143" s="1" t="s">
         <v>448</v>
       </c>
       <c r="E143" s="1">
@@ -8408,7 +8404,7 @@
       <c r="C144" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="D144" s="2" t="s">
+      <c r="D144" s="1" t="s">
         <v>451</v>
       </c>
       <c r="E144" s="1">
@@ -8452,7 +8448,7 @@
       <c r="C145" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="D145" s="2" t="s">
+      <c r="D145" s="1" t="s">
         <v>454</v>
       </c>
       <c r="E145" s="1">
@@ -8496,7 +8492,7 @@
       <c r="C146" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="D146" s="2" t="s">
+      <c r="D146" s="1" t="s">
         <v>457</v>
       </c>
       <c r="E146" s="1">
@@ -8540,7 +8536,7 @@
       <c r="C147" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="D147" s="2" t="s">
+      <c r="D147" s="1" t="s">
         <v>460</v>
       </c>
       <c r="E147" s="1">
@@ -8584,7 +8580,7 @@
       <c r="C148" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="D148" s="2" t="s">
+      <c r="D148" s="1" t="s">
         <v>463</v>
       </c>
       <c r="E148" s="1">
@@ -8628,7 +8624,7 @@
       <c r="C149" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="D149" s="2" t="s">
+      <c r="D149" s="1" t="s">
         <v>466</v>
       </c>
       <c r="E149" s="1">
@@ -8672,7 +8668,7 @@
       <c r="C150" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="D150" s="2" t="s">
+      <c r="D150" s="1" t="s">
         <v>469</v>
       </c>
       <c r="E150" s="1">
@@ -8716,7 +8712,7 @@
       <c r="C151" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="D151" s="2" t="s">
+      <c r="D151" s="1" t="s">
         <v>472</v>
       </c>
       <c r="E151" s="1">
@@ -8760,7 +8756,7 @@
       <c r="C152" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="D152" s="2" t="s">
+      <c r="D152" s="1" t="s">
         <v>475</v>
       </c>
       <c r="E152" s="1">
@@ -8804,7 +8800,7 @@
       <c r="C153" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="D153" s="2" t="s">
+      <c r="D153" s="1" t="s">
         <v>478</v>
       </c>
       <c r="E153" s="1">
@@ -8848,7 +8844,7 @@
       <c r="C154" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="D154" s="2" t="s">
+      <c r="D154" s="1" t="s">
         <v>481</v>
       </c>
       <c r="E154" s="1">
@@ -8892,7 +8888,7 @@
       <c r="C155" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="D155" s="2" t="s">
+      <c r="D155" s="1" t="s">
         <v>484</v>
       </c>
       <c r="E155" s="1">
@@ -8936,7 +8932,7 @@
       <c r="C156" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="D156" s="2" t="s">
+      <c r="D156" s="1" t="s">
         <v>487</v>
       </c>
       <c r="E156" s="1">
@@ -8977,7 +8973,7 @@
       <c r="B157" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="D157" s="2" t="s">
+      <c r="D157" s="1" t="s">
         <v>491</v>
       </c>
       <c r="E157" s="1">
@@ -9015,7 +9011,7 @@
       <c r="B158" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="D158" s="2" t="s">
+      <c r="D158" s="1" t="s">
         <v>494</v>
       </c>
       <c r="E158" s="1">
@@ -9053,7 +9049,7 @@
       <c r="B159" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="D159" s="2" t="s">
+      <c r="D159" s="1" t="s">
         <v>496</v>
       </c>
       <c r="E159" s="1">
@@ -9091,7 +9087,7 @@
       <c r="B160" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="D160" s="2" t="s">
+      <c r="D160" s="1" t="s">
         <v>498</v>
       </c>
       <c r="E160" s="1">
@@ -9129,7 +9125,7 @@
       <c r="B161" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D161" s="2" t="s">
+      <c r="D161" s="1" t="s">
         <v>500</v>
       </c>
       <c r="E161" s="1">
@@ -9167,7 +9163,7 @@
       <c r="B162" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="D162" s="2" t="s">
+      <c r="D162" s="1" t="s">
         <v>502</v>
       </c>
       <c r="E162" s="1">
@@ -9205,7 +9201,7 @@
       <c r="B163" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="D163" s="2" t="s">
+      <c r="D163" s="1" t="s">
         <v>504</v>
       </c>
       <c r="E163" s="1">
@@ -9243,7 +9239,7 @@
       <c r="B164" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="D164" s="2" t="s">
+      <c r="D164" s="1" t="s">
         <v>506</v>
       </c>
       <c r="E164" s="1">
@@ -9281,7 +9277,7 @@
       <c r="B165" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="D165" s="2" t="s">
+      <c r="D165" s="1" t="s">
         <v>508</v>
       </c>
       <c r="E165" s="1">
@@ -9319,7 +9315,7 @@
       <c r="B166" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D166" s="2" t="s">
+      <c r="D166" s="1" t="s">
         <v>510</v>
       </c>
       <c r="E166" s="1">
@@ -9357,7 +9353,7 @@
       <c r="B167" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="D167" s="2" t="s">
+      <c r="D167" s="1" t="s">
         <v>512</v>
       </c>
       <c r="E167" s="1">
@@ -9395,7 +9391,7 @@
       <c r="B168" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="D168" s="2" t="s">
+      <c r="D168" s="1" t="s">
         <v>514</v>
       </c>
       <c r="E168" s="1">
@@ -9433,7 +9429,7 @@
       <c r="B169" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="D169" s="2" t="s">
+      <c r="D169" s="1" t="s">
         <v>516</v>
       </c>
       <c r="E169" s="1">
@@ -9471,7 +9467,7 @@
       <c r="B170" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="D170" s="2" t="s">
+      <c r="D170" s="1" t="s">
         <v>518</v>
       </c>
       <c r="E170" s="1">
@@ -9509,7 +9505,7 @@
       <c r="B171" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="D171" s="2" t="s">
+      <c r="D171" s="1" t="s">
         <v>520</v>
       </c>
       <c r="E171" s="1">
@@ -9547,7 +9543,7 @@
       <c r="B172" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="D172" s="2" t="s">
+      <c r="D172" s="1" t="s">
         <v>522</v>
       </c>
       <c r="E172" s="1">
@@ -9585,7 +9581,7 @@
       <c r="B173" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="D173" s="2" t="s">
+      <c r="D173" s="1" t="s">
         <v>524</v>
       </c>
       <c r="E173" s="1">
@@ -9623,7 +9619,7 @@
       <c r="B174" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="D174" s="2" t="s">
+      <c r="D174" s="1" t="s">
         <v>526</v>
       </c>
       <c r="E174" s="1">
@@ -9661,7 +9657,7 @@
       <c r="B175" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="D175" s="2" t="s">
+      <c r="D175" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E175" s="1">
@@ -9699,7 +9695,7 @@
       <c r="B176" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="D176" s="2" t="s">
+      <c r="D176" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E176" s="1">
@@ -9737,7 +9733,7 @@
       <c r="B177" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="D177" s="2" t="s">
+      <c r="D177" s="1" t="s">
         <v>532</v>
       </c>
       <c r="E177" s="1">
@@ -9775,7 +9771,7 @@
       <c r="B178" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="D178" s="2" t="s">
+      <c r="D178" s="1" t="s">
         <v>534</v>
       </c>
       <c r="E178" s="1">
@@ -9813,7 +9809,7 @@
       <c r="B179" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="D179" s="2" t="s">
+      <c r="D179" s="1" t="s">
         <v>536</v>
       </c>
       <c r="E179" s="1">
@@ -9851,7 +9847,7 @@
       <c r="B180" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D180" s="2" t="s">
+      <c r="D180" s="1" t="s">
         <v>538</v>
       </c>
       <c r="E180" s="1">
@@ -9889,7 +9885,7 @@
       <c r="B181" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="D181" s="2" t="s">
+      <c r="D181" s="1" t="s">
         <v>540</v>
       </c>
       <c r="E181" s="1">
@@ -9927,7 +9923,7 @@
       <c r="B182" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="D182" s="2" t="s">
+      <c r="D182" s="1" t="s">
         <v>542</v>
       </c>
       <c r="E182" s="1">
@@ -9965,7 +9961,7 @@
       <c r="B183" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="D183" s="2" t="s">
+      <c r="D183" s="1" t="s">
         <v>544</v>
       </c>
       <c r="E183" s="1">
@@ -10003,7 +9999,7 @@
       <c r="B184" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="D184" s="2" t="s">
+      <c r="D184" s="1" t="s">
         <v>546</v>
       </c>
       <c r="E184" s="1">
@@ -10041,7 +10037,7 @@
       <c r="B185" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="D185" s="2" t="s">
+      <c r="D185" s="1" t="s">
         <v>548</v>
       </c>
       <c r="E185" s="1">
@@ -10079,7 +10075,7 @@
       <c r="B186" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="D186" s="2" t="s">
+      <c r="D186" s="1" t="s">
         <v>550</v>
       </c>
       <c r="E186" s="1">
@@ -10117,7 +10113,7 @@
       <c r="B187" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="D187" s="2" t="s">
+      <c r="D187" s="1" t="s">
         <v>552</v>
       </c>
       <c r="E187" s="1">
@@ -10155,7 +10151,7 @@
       <c r="B188" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="D188" s="2" t="s">
+      <c r="D188" s="1" t="s">
         <v>554</v>
       </c>
       <c r="E188" s="1">
@@ -10193,7 +10189,7 @@
       <c r="B189" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="D189" s="2" t="s">
+      <c r="D189" s="1" t="s">
         <v>556</v>
       </c>
       <c r="E189" s="1">
@@ -10231,7 +10227,7 @@
       <c r="B190" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="D190" s="2" t="s">
+      <c r="D190" s="1" t="s">
         <v>558</v>
       </c>
       <c r="E190" s="1">
@@ -10269,7 +10265,7 @@
       <c r="B191" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="D191" s="2" t="s">
+      <c r="D191" s="1" t="s">
         <v>561</v>
       </c>
       <c r="E191" s="1">
@@ -10307,7 +10303,7 @@
       <c r="B192" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="D192" s="2" t="s">
+      <c r="D192" s="1" t="s">
         <v>563</v>
       </c>
       <c r="E192" s="1">
@@ -10345,7 +10341,7 @@
       <c r="B193" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="D193" s="2" t="s">
+      <c r="D193" s="1" t="s">
         <v>565</v>
       </c>
       <c r="E193" s="1">
@@ -10383,7 +10379,7 @@
       <c r="B194" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="D194" s="2" t="s">
+      <c r="D194" s="1" t="s">
         <v>567</v>
       </c>
       <c r="E194" s="1">
@@ -10421,7 +10417,7 @@
       <c r="B195" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="D195" s="2" t="s">
+      <c r="D195" s="1" t="s">
         <v>569</v>
       </c>
       <c r="E195" s="1">
@@ -10459,7 +10455,7 @@
       <c r="B196" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="D196" s="2" t="s">
+      <c r="D196" s="1" t="s">
         <v>571</v>
       </c>
       <c r="E196" s="1">
@@ -10497,7 +10493,7 @@
       <c r="B197" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="D197" s="2" t="s">
+      <c r="D197" s="1" t="s">
         <v>573</v>
       </c>
       <c r="E197" s="1">
@@ -10535,7 +10531,7 @@
       <c r="B198" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="D198" s="2" t="s">
+      <c r="D198" s="1" t="s">
         <v>575</v>
       </c>
       <c r="E198" s="1">
@@ -10573,7 +10569,7 @@
       <c r="B199" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="D199" s="2" t="s">
+      <c r="D199" s="1" t="s">
         <v>577</v>
       </c>
       <c r="E199" s="1">
@@ -10611,7 +10607,7 @@
       <c r="B200" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="D200" s="2" t="s">
+      <c r="D200" s="1" t="s">
         <v>579</v>
       </c>
       <c r="E200" s="1">
@@ -10649,7 +10645,7 @@
       <c r="B201" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="D201" s="2" t="s">
+      <c r="D201" s="1" t="s">
         <v>581</v>
       </c>
       <c r="E201" s="1">
@@ -10687,7 +10683,7 @@
       <c r="B202" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="D202" s="2" t="s">
+      <c r="D202" s="1" t="s">
         <v>583</v>
       </c>
       <c r="E202" s="1">
@@ -10725,7 +10721,7 @@
       <c r="B203" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="D203" s="2" t="s">
+      <c r="D203" s="1" t="s">
         <v>585</v>
       </c>
       <c r="E203" s="1">
@@ -10763,7 +10759,7 @@
       <c r="B204" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="D204" s="2" t="s">
+      <c r="D204" s="1" t="s">
         <v>587</v>
       </c>
       <c r="E204" s="1">
@@ -10801,7 +10797,7 @@
       <c r="B205" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="D205" s="2" t="s">
+      <c r="D205" s="1" t="s">
         <v>589</v>
       </c>
       <c r="E205" s="1">
@@ -10839,7 +10835,7 @@
       <c r="B206" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="D206" s="2" t="s">
+      <c r="D206" s="1" t="s">
         <v>591</v>
       </c>
       <c r="E206" s="1">
@@ -10877,7 +10873,7 @@
       <c r="B207" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="D207" s="2" t="s">
+      <c r="D207" s="1" t="s">
         <v>593</v>
       </c>
       <c r="E207" s="1">
@@ -10915,7 +10911,7 @@
       <c r="B208" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="D208" s="2" t="s">
+      <c r="D208" s="1" t="s">
         <v>595</v>
       </c>
       <c r="E208" s="1">
@@ -10953,7 +10949,7 @@
       <c r="B209" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="D209" s="2" t="s">
+      <c r="D209" s="1" t="s">
         <v>597</v>
       </c>
       <c r="E209" s="1">
@@ -10991,7 +10987,7 @@
       <c r="B210" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="D210" s="2" t="s">
+      <c r="D210" s="1" t="s">
         <v>599</v>
       </c>
       <c r="E210" s="1">
@@ -11029,7 +11025,7 @@
       <c r="B211" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="D211" s="2" t="s">
+      <c r="D211" s="1" t="s">
         <v>601</v>
       </c>
       <c r="E211" s="1">
@@ -11067,7 +11063,7 @@
       <c r="B212" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="D212" s="2" t="s">
+      <c r="D212" s="1" t="s">
         <v>603</v>
       </c>
       <c r="E212" s="1">
@@ -11105,7 +11101,7 @@
       <c r="B213" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="D213" s="2" t="s">
+      <c r="D213" s="1" t="s">
         <v>605</v>
       </c>
       <c r="E213" s="1">
@@ -11921,6 +11917,8 @@
     <row r="996" ht="15.75" customHeight="1"/>
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>

--- a/main/upload/upload.xlsx
+++ b/main/upload/upload.xlsx
@@ -58,7 +58,7 @@
     <t>Опубликован</t>
   </si>
   <si>
-    <t>Комбинированые модели</t>
+    <t>Комбинированые памятники</t>
   </si>
   <si>
     <t>Стелла</t>
@@ -274,7 +274,7 @@
     <t>5.135</t>
   </si>
   <si>
-    <t>Элитные модели</t>
+    <t>Элитные памятники</t>
   </si>
   <si>
     <t>25E</t>
@@ -466,7 +466,7 @@
     <t>5.114</t>
   </si>
   <si>
-    <t>Двойный модели</t>
+    <t>Двойный памятники</t>
   </si>
   <si>
     <t>126.0</t>
@@ -487,7 +487,7 @@
     <t>5.112</t>
   </si>
   <si>
-    <t>Фигурные модели</t>
+    <t>Фигурные памятники</t>
   </si>
   <si>
     <t>124.0</t>
@@ -1861,11 +1861,14 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -2147,7 +2150,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -2191,7 +2194,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -2235,7 +2238,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -2279,7 +2282,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -2323,7 +2326,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -2367,7 +2370,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -2411,7 +2414,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -2455,7 +2458,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -2499,7 +2502,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -2543,7 +2546,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -2587,7 +2590,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -2631,7 +2634,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -2675,7 +2678,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -2719,7 +2722,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -2763,7 +2766,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -2807,7 +2810,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -2851,7 +2854,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -2895,7 +2898,7 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -2939,7 +2942,7 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -2983,7 +2986,7 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -3027,7 +3030,7 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -3071,7 +3074,7 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -3115,7 +3118,7 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -3159,7 +3162,7 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -3203,7 +3206,7 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -3247,7 +3250,7 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -3291,7 +3294,7 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -3335,7 +3338,7 @@
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -3379,7 +3382,7 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -3423,7 +3426,7 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -3467,7 +3470,7 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -3511,7 +3514,7 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -3555,7 +3558,7 @@
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -3599,7 +3602,7 @@
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -3643,7 +3646,7 @@
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -3687,7 +3690,7 @@
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -3731,7 +3734,7 @@
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -3775,7 +3778,7 @@
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -3819,7 +3822,7 @@
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -3863,7 +3866,7 @@
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -3907,7 +3910,7 @@
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -3951,7 +3954,7 @@
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -3995,7 +3998,7 @@
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -4039,7 +4042,7 @@
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -4083,7 +4086,7 @@
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -4127,7 +4130,7 @@
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -4171,7 +4174,7 @@
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -4215,7 +4218,7 @@
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -4259,7 +4262,7 @@
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B50" s="1" t="s">
@@ -4303,7 +4306,7 @@
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -4347,7 +4350,7 @@
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B52" s="1" t="s">
@@ -4391,7 +4394,7 @@
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B53" s="1" t="s">
@@ -4435,7 +4438,7 @@
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B54" s="1" t="s">
@@ -4479,7 +4482,7 @@
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -4523,7 +4526,7 @@
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B56" s="1" t="s">
@@ -4567,7 +4570,7 @@
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B57" s="1" t="s">
@@ -4611,7 +4614,7 @@
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B58" s="1" t="s">
@@ -4655,7 +4658,7 @@
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -4699,7 +4702,7 @@
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B60" s="1" t="s">
@@ -4743,7 +4746,7 @@
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B61" s="1" t="s">
@@ -4787,7 +4790,7 @@
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B62" s="1" t="s">
@@ -4831,7 +4834,7 @@
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -4875,7 +4878,7 @@
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B64" s="1" t="s">
@@ -4919,7 +4922,7 @@
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B65" s="1" t="s">
@@ -4963,7 +4966,7 @@
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="1" t="s">
+      <c r="A66" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B66" s="1" t="s">
@@ -5007,7 +5010,7 @@
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B67" s="1" t="s">
@@ -5051,7 +5054,7 @@
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="1" t="s">
+      <c r="A68" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B68" s="1" t="s">
@@ -5095,7 +5098,7 @@
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B69" s="1" t="s">
@@ -5139,7 +5142,7 @@
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B70" s="1" t="s">
@@ -5183,7 +5186,7 @@
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B71" s="1" t="s">
@@ -5227,7 +5230,7 @@
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B72" s="1" t="s">
@@ -5271,7 +5274,7 @@
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B73" s="1" t="s">
@@ -5315,7 +5318,7 @@
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="1" t="s">
+      <c r="A74" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B74" s="1" t="s">
@@ -5359,7 +5362,7 @@
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B75" s="1" t="s">
@@ -5403,7 +5406,7 @@
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="1" t="s">
+      <c r="A76" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B76" s="1" t="s">
@@ -5447,7 +5450,7 @@
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="1" t="s">
+      <c r="A77" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B77" s="1" t="s">
@@ -5491,7 +5494,7 @@
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="1" t="s">
+      <c r="A78" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B78" s="1" t="s">
@@ -5535,7 +5538,7 @@
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B79" s="1" t="s">
@@ -5579,7 +5582,7 @@
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="1" t="s">
+      <c r="A80" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B80" s="1" t="s">
@@ -5623,7 +5626,7 @@
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="1" t="s">
+      <c r="A81" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B81" s="1" t="s">
@@ -5667,7 +5670,7 @@
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="1" t="s">
+      <c r="A82" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B82" s="1" t="s">
@@ -5711,7 +5714,7 @@
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="1" t="s">
+      <c r="A83" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B83" s="1" t="s">
@@ -5755,7 +5758,7 @@
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="1" t="s">
+      <c r="A84" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B84" s="1" t="s">
@@ -5799,7 +5802,7 @@
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="1" t="s">
+      <c r="A85" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B85" s="1" t="s">
@@ -5843,7 +5846,7 @@
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="1" t="s">
+      <c r="A86" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B86" s="1" t="s">
@@ -5887,7 +5890,7 @@
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="1" t="s">
+      <c r="A87" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B87" s="1" t="s">
@@ -5931,7 +5934,7 @@
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="1" t="s">
+      <c r="A88" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B88" s="1" t="s">
@@ -5975,7 +5978,7 @@
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="1" t="s">
+      <c r="A89" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B89" s="1" t="s">
@@ -6019,7 +6022,7 @@
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="1" t="s">
+      <c r="A90" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B90" s="1" t="s">
@@ -6063,7 +6066,7 @@
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="1" t="s">
+      <c r="A91" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B91" s="1" t="s">
@@ -6107,7 +6110,7 @@
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="1" t="s">
+      <c r="A92" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B92" s="1" t="s">
@@ -6151,7 +6154,7 @@
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="1" t="s">
+      <c r="A93" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B93" s="1" t="s">
@@ -6195,7 +6198,7 @@
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="1" t="s">
+      <c r="A94" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B94" s="1" t="s">
@@ -6239,7 +6242,7 @@
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="1" t="s">
+      <c r="A95" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B95" s="1" t="s">
@@ -6283,7 +6286,7 @@
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="1" t="s">
+      <c r="A96" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B96" s="1" t="s">
@@ -6327,7 +6330,7 @@
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="1" t="s">
+      <c r="A97" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B97" s="1" t="s">
@@ -6371,7 +6374,7 @@
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="1" t="s">
+      <c r="A98" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B98" s="1" t="s">
@@ -6415,7 +6418,7 @@
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="1" t="s">
+      <c r="A99" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B99" s="1" t="s">
@@ -6459,7 +6462,7 @@
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="1" t="s">
+      <c r="A100" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B100" s="1" t="s">
@@ -6503,7 +6506,7 @@
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="1" t="s">
+      <c r="A101" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B101" s="1" t="s">
@@ -6547,7 +6550,7 @@
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="1" t="s">
+      <c r="A102" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B102" s="1" t="s">
@@ -6591,7 +6594,7 @@
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="1" t="s">
+      <c r="A103" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B103" s="1" t="s">
@@ -6635,7 +6638,7 @@
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="1" t="s">
+      <c r="A104" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B104" s="1" t="s">
@@ -6679,7 +6682,7 @@
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="1" t="s">
+      <c r="A105" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B105" s="1" t="s">
@@ -6723,7 +6726,7 @@
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="1" t="s">
+      <c r="A106" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B106" s="1" t="s">
@@ -6767,7 +6770,7 @@
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="1" t="s">
+      <c r="A107" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B107" s="1" t="s">
@@ -6811,7 +6814,7 @@
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="1" t="s">
+      <c r="A108" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B108" s="1" t="s">
@@ -6855,7 +6858,7 @@
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="1" t="s">
+      <c r="A109" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B109" s="1" t="s">
@@ -6899,7 +6902,7 @@
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="1" t="s">
+      <c r="A110" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B110" s="1" t="s">
@@ -6943,7 +6946,7 @@
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="1" t="s">
+      <c r="A111" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B111" s="1" t="s">
@@ -6987,7 +6990,7 @@
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="1" t="s">
+      <c r="A112" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B112" s="1" t="s">
@@ -7031,7 +7034,7 @@
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="1" t="s">
+      <c r="A113" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B113" s="1" t="s">
@@ -7075,7 +7078,7 @@
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="1" t="s">
+      <c r="A114" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B114" s="1" t="s">
@@ -7119,7 +7122,7 @@
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="1" t="s">
+      <c r="A115" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B115" s="1" t="s">
@@ -7163,7 +7166,7 @@
       </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="1" t="s">
+      <c r="A116" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B116" s="1" t="s">
@@ -7207,7 +7210,7 @@
       </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="1" t="s">
+      <c r="A117" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B117" s="1" t="s">
@@ -7251,7 +7254,7 @@
       </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="1" t="s">
+      <c r="A118" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B118" s="1" t="s">
@@ -7295,7 +7298,7 @@
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="1" t="s">
+      <c r="A119" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B119" s="1" t="s">
@@ -7339,7 +7342,7 @@
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="1" t="s">
+      <c r="A120" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B120" s="1" t="s">
@@ -7383,7 +7386,7 @@
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="1" t="s">
+      <c r="A121" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B121" s="1" t="s">
@@ -7427,7 +7430,7 @@
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="1" t="s">
+      <c r="A122" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B122" s="1" t="s">
@@ -7471,7 +7474,7 @@
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="1" t="s">
+      <c r="A123" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B123" s="1" t="s">
@@ -7515,7 +7518,7 @@
       </c>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="1" t="s">
+      <c r="A124" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B124" s="1" t="s">
@@ -7559,7 +7562,7 @@
       </c>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="1" t="s">
+      <c r="A125" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B125" s="1" t="s">
@@ -7603,7 +7606,7 @@
       </c>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="1" t="s">
+      <c r="A126" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B126" s="1" t="s">
@@ -7647,7 +7650,7 @@
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="1" t="s">
+      <c r="A127" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B127" s="1" t="s">
@@ -7691,7 +7694,7 @@
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="1" t="s">
+      <c r="A128" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B128" s="1" t="s">
@@ -7735,7 +7738,7 @@
       </c>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="1" t="s">
+      <c r="A129" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B129" s="1" t="s">
@@ -7779,7 +7782,7 @@
       </c>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="1" t="s">
+      <c r="A130" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B130" s="1" t="s">
@@ -7823,7 +7826,7 @@
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="1" t="s">
+      <c r="A131" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B131" s="1" t="s">
@@ -7867,7 +7870,7 @@
       </c>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="1" t="s">
+      <c r="A132" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B132" s="1" t="s">
@@ -7911,7 +7914,7 @@
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="1" t="s">
+      <c r="A133" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B133" s="1" t="s">
@@ -7955,7 +7958,7 @@
       </c>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="1" t="s">
+      <c r="A134" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B134" s="1" t="s">
@@ -7999,7 +8002,7 @@
       </c>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="1" t="s">
+      <c r="A135" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B135" s="1" t="s">
@@ -8043,7 +8046,7 @@
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="1" t="s">
+      <c r="A136" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B136" s="1" t="s">
@@ -8087,7 +8090,7 @@
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="1" t="s">
+      <c r="A137" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B137" s="1" t="s">
@@ -8131,7 +8134,7 @@
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="1" t="s">
+      <c r="A138" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B138" s="1" t="s">
@@ -8175,7 +8178,7 @@
       </c>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="1" t="s">
+      <c r="A139" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B139" s="1" t="s">
@@ -8219,7 +8222,7 @@
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="1" t="s">
+      <c r="A140" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B140" s="1" t="s">
@@ -8263,7 +8266,7 @@
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="1" t="s">
+      <c r="A141" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B141" s="1" t="s">
@@ -8307,7 +8310,7 @@
       </c>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="1" t="s">
+      <c r="A142" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B142" s="1" t="s">
@@ -8351,7 +8354,7 @@
       </c>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="1" t="s">
+      <c r="A143" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B143" s="1" t="s">
@@ -8395,7 +8398,7 @@
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="1" t="s">
+      <c r="A144" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B144" s="1" t="s">
@@ -8439,7 +8442,7 @@
       </c>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="1" t="s">
+      <c r="A145" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B145" s="1" t="s">
@@ -8483,7 +8486,7 @@
       </c>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="1" t="s">
+      <c r="A146" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B146" s="1" t="s">
@@ -8527,7 +8530,7 @@
       </c>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="1" t="s">
+      <c r="A147" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B147" s="1" t="s">
@@ -8571,7 +8574,7 @@
       </c>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="1" t="s">
+      <c r="A148" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B148" s="1" t="s">
@@ -8615,7 +8618,7 @@
       </c>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="1" t="s">
+      <c r="A149" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B149" s="1" t="s">
@@ -8659,7 +8662,7 @@
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="1" t="s">
+      <c r="A150" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B150" s="1" t="s">
@@ -8703,7 +8706,7 @@
       </c>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="1" t="s">
+      <c r="A151" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B151" s="1" t="s">
@@ -8747,7 +8750,7 @@
       </c>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="1" t="s">
+      <c r="A152" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B152" s="1" t="s">
@@ -8791,7 +8794,7 @@
       </c>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="1" t="s">
+      <c r="A153" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B153" s="1" t="s">
@@ -8835,7 +8838,7 @@
       </c>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="1" t="s">
+      <c r="A154" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B154" s="1" t="s">
@@ -8879,7 +8882,7 @@
       </c>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="1" t="s">
+      <c r="A155" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B155" s="1" t="s">
@@ -8923,7 +8926,7 @@
       </c>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="1" t="s">
+      <c r="A156" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B156" s="1" t="s">
